--- a/safety_inspection_forms/022_gate_control_checklist--safety_inspection_forms.xlsx
+++ b/safety_inspection_forms/022_gate_control_checklist--safety_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'access_point_1'}</t>
+          <t>access_point_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Access Point 1'}</t>
+          <t>Access Point 1</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'access_point_2'}</t>
+          <t>access_point_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Access Point 2'}</t>
+          <t>Access Point 2</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'unavailable'}</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Unavailable'}</t>
+          <t>Unavailable</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1140,12 +1140,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'accept'}</t>
+          <t>accept</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Accept'}</t>
+          <t>Accept</t>
         </is>
       </c>
     </row>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'reject'}</t>
+          <t>reject</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Reject'}</t>
+          <t>Reject</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'done'}</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Done'}</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1191,12 +1191,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_done'}</t>
+          <t>not_done</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not done'}</t>
+          <t>Not done</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1225,12 +1225,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'closed'}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Closed'}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
